--- a/2_공통코드_샘플.xlsx
+++ b/2_공통코드_샘플.xlsx
@@ -91,64 +91,64 @@
     <t>REVIEW_STAT</t>
   </si>
   <si>
-    <t>MEMBER_GRADE_GRP</t>
-  </si>
-  <si>
-    <t>MEMBER_STAT_GRP</t>
-  </si>
-  <si>
-    <t>PROD_TYPE_GRP</t>
-  </si>
-  <si>
-    <t>SALE_STAT_GRP</t>
-  </si>
-  <si>
-    <t>CAT_STAT_GRP</t>
-  </si>
-  <si>
-    <t>DISP_YN_GRP</t>
-  </si>
-  <si>
-    <t>ORDER_STAT_GRP</t>
-  </si>
-  <si>
-    <t>PAY_METHOD_GRP</t>
-  </si>
-  <si>
-    <t>ITEM_STAT_GRP</t>
-  </si>
-  <si>
-    <t>CLAIM_TYPE_GRP</t>
-  </si>
-  <si>
-    <t>PAY_TYPE_GRP</t>
-  </si>
-  <si>
-    <t>PAY_STAT_GRP</t>
-  </si>
-  <si>
-    <t>DELIV_STAT_GRP</t>
-  </si>
-  <si>
-    <t>DELIV_CORP_GRP</t>
-  </si>
-  <si>
-    <t>COUPON_TYPE_GRP</t>
-  </si>
-  <si>
-    <t>COUPON_STAT_GRP</t>
-  </si>
-  <si>
-    <t>POINT_TYPE_GRP</t>
-  </si>
-  <si>
-    <t>POINT_STAT_GRP</t>
-  </si>
-  <si>
-    <t>RATING_SCORE_GRP</t>
-  </si>
-  <si>
-    <t>REVIEW_STAT_GRP</t>
+    <t>001</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>020</t>
   </si>
   <si>
     <t>회원등급그룹</t>
